--- a/InputFiles/C3DC/TC01_C3DC_Study_Accession_phs000467_SexAtBirth-Male_Race-Asian.xlsx
+++ b/InputFiles/C3DC/TC01_C3DC_Study_Accession_phs000467_SexAtBirth-Male_Race-Asian.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sohilz2/Automation/c3dc-04-05-24/Commons_Automation/InputFiles/C3DC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epishinavv\git\Commons_Automation\InputFiles\C3DC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE90BB36-C2CE-FF4D-B67B-6C0E0C30C901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E1ACE0-A278-4149-9826-76CF1CFEB2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38780" yWindow="2920" windowWidth="23260" windowHeight="12580" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10180" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
   </bookViews>
   <sheets>
     <sheet name="startup" sheetId="1" r:id="rId1"/>
@@ -507,16 +507,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C538400-E87C-4027-A918-A51DB80B3430}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="72.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="63.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="62.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="72.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="63.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -533,7 +533,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="208" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -550,7 +550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="240" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -567,7 +567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="192" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="174" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -584,7 +584,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="208" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -601,7 +601,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C6" s="1"/>
     </row>
   </sheetData>
